--- a/20260804_従業員管理_01_確認表.xlsx
+++ b/20260804_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認表'!$A$7:$M$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認表'!$A$7:$M$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>COUNTIFS(B8:B54,"L0*",J8:J54,"合格")&amp;" / "&amp;COUNTIF(B8:B54,"L0*")&amp;" 合格"</f>
+        <f>COUNTIFS(B8:B58,"L0*",J8:J58,"合格")&amp;" / "&amp;COUNTIF(B8:B58,"L0*")&amp;" 合格"</f>
         <v/>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIFS(I8:I54,"★中止",J8:J54,"合格")+COUNTIFS(I8:I54,"不可",J8:J54,"合格")&amp;" / "&amp;(COUNTIF(I8:I54,"★中止")+COUNTIF(I8:I54,"不可"))&amp;" 合格"</f>
+        <f>COUNTIFS(I8:I58,"★中止",J8:J58,"合格")+COUNTIFS(I8:I58,"不可",J8:J58,"合格")&amp;" / "&amp;(COUNTIF(I8:I58,"★中止")+COUNTIF(I8:I58,"不可"))&amp;" 合格"</f>
         <v/>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>IF(COUNTIFS(B8:B54,"L0*",J8:J54,"合格")&lt;COUNTIF(B8:B54,"L0*"),"✗ No-Go ／ L0が未達",IF(COUNTIFS(I8:I54,"不可",J8:J54,"合格")&lt;COUNTIF(I8:I54,"不可"),"△ 設計MVP未達 ／ 落とせない条件が残っている",IF(COUNTIFS(I8:I54,"条件付きGo可",J8:J54,"合格")&lt;COUNTIF(I8:I54,"条件付きGo可"),"◯ 条件付きGo ／ 残りは手作業で代替","◎ Go ／ すべて合格")))</f>
+        <f>IF(COUNTIFS(B8:B58,"L0*",J8:J58,"合格")&lt;COUNTIF(B8:B58,"L0*"),"✗ No-Go ／ L0が未達",IF(COUNTIFS(I8:I58,"不可",J8:J58,"合格")&lt;COUNTIF(I8:I58,"不可"),"△ 設計MVP未達 ／ 落とせない条件が残っている",IF(COUNTIFS(I8:I58,"条件付きGo可",J8:J58,"合格")&lt;COUNTIF(I8:I58,"条件付きGo可"),"◯ 条件付きGo ／ 残りは手作業で代替","◎ Go ／ すべて合格")))</f>
         <v/>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>T-D08 T-E04 T-H04 T-I02 T-I09 T-L06 T-R07 T-Z05</t>
+          <t>T-D08 T-E04 T-H04 T-I02 T-I09 T-L06 T-N03 T-R07 T-Z05</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
@@ -3089,8 +3089,212 @@
       <c r="L54" s="11" t="inlineStr"/>
       <c r="M54" s="11" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>AC-48</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>実装M2 計算エンジン</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>「実績データ取込」で勤怠実績が取り込まれ、人件費実績に反映されること</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>取込後に実績モードの金額が表示される（未反映=0件）。取込中は画面を操作できない</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>T-A08</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>操作で確認</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr"/>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>実装M1 データ基盤</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>人件費実績（設定編集モーダル）／従業員詳細</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>どの入口から設定を編集しても、適用日付と設定変更履歴が同じように記録されること</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>T-A09 R-06</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>操作＋実装レビュー</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr"/>
+      <c r="L56" s="11" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>AC-50</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>実装M4 画面・入出力</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>取り込む前に、内容のプレビューと前回との差分を確認できること</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>プレビューで取込内容が表示される。前回差分で「前回◯◯→新規◯◯」の形式で差が表示される（差分が出ない=0件）</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>T-N02</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>操作で確認</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>条件付きGo可</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr"/>
+      <c r="K57" s="11" t="inlineStr"/>
+      <c r="L57" s="11" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>AC-51</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>L2 次段階</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>（次リリース）</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>マッピング表をテンプレートでダウンロードし、行を追加・更新できること</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>テンプレートDL・行追加・更新がいずれも動作（失敗=0）</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>操作で確認</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>影響なし</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr"/>
+      <c r="K58" s="11" t="inlineStr"/>
+      <c r="L58" s="11" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:M54"/>
+  <autoFilter ref="A7:M58"/>
   <mergeCells count="5">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="B4:E4"/>
@@ -3098,7 +3302,7 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J8:J54">
+  <conditionalFormatting sqref="J8:J58">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"合格"</formula>
     </cfRule>
@@ -3107,7 +3311,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J8:J54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J8:J58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未実装"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_従業員管理_01_確認表.xlsx
+++ b/20260804_従業員管理_01_確認表.xlsx
@@ -1944,7 +1944,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>選択時の手入力=0項目</t>
+          <t>保存済みテンプレート選択時の手入力=0項目。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>テンプレートDL・行追加・更新がいずれも動作（失敗=0）</t>
+          <t>テンプレートDL・アップロード（CSV最大10MB）・行を追加・更新する がいずれも動作（失敗=0）。10MB超は拒否</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
